--- a/互联网医疗中心平台_项目状态报告.xlsx
+++ b/互联网医疗中心平台_项目状态报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18345" windowHeight="9675"/>
+    <workbookView windowWidth="18345" windowHeight="9675" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="项目概况仪表板" sheetId="1" r:id="rId1"/>
@@ -3188,7 +3188,7 @@
     <col min="1" max="1" width="7.00833333333333" customWidth="1"/>
     <col min="2" max="2" width="14.0083333333333" customWidth="1"/>
     <col min="3" max="3" width="8.675" customWidth="1"/>
-    <col min="4" max="4" width="50.625" customWidth="1"/>
+    <col min="4" max="4" width="53" customWidth="1"/>
     <col min="5" max="5" width="19.4916666666667" customWidth="1"/>
     <col min="6" max="6" width="15.325" customWidth="1"/>
   </cols>

--- a/互联网医疗中心平台_项目状态报告.xlsx
+++ b/互联网医疗中心平台_项目状态报告.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18345" windowHeight="9675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18345" windowHeight="9675" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目概况仪表板" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="41">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -144,13 +144,6 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -300,21 +293,20 @@
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color rgb="FFB7780B"/>
+      <color rgb="FF1B7A3D"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFB7780B"/>
+      <color theme="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color rgb="FF1B7A3D"/>
+      <color rgb="FFB7780B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -579,7 +571,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -603,9 +595,59 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FFF39C12"/>
       </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFDDDDDD"/>
       </right>
@@ -767,19 +809,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFCCCCCC"/>
@@ -798,186 +827,159 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="13" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="14" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="39" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="41" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="42" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1000,114 +1002,156 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1527,802 +1571,791 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F40"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="39.5" defaultRowHeight="13.5"/>
   <cols>
-    <col width="18.3416666666667" customWidth="1" min="1" max="1"/>
-    <col width="35.3416666666667" customWidth="1" min="2" max="2"/>
-    <col width="23.175" customWidth="1" min="3" max="3"/>
-    <col width="43.0083333333333" customWidth="1" min="4" max="4"/>
-    <col width="12.3416666666667" customWidth="1" min="5" max="5"/>
-    <col width="10.5083333333333" customWidth="1" min="6" max="6"/>
+    <col width="39.5" customWidth="1" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
-      <c r="A1" s="9" t="n"/>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
+      <c r="A1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="29" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>互联网医疗中心平台 · 项目状态报告</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="29" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>报告日期：2026-08-01　|　文档版本：V1.1　|　基线：PRD V2.0 / 技术架构 V1.2　|　编制：项目管理</t>
+      <c r="A3" s="26" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>报告日期：2026-08-03｜文档版本：V1.2｜基线：PRD V2.0 / 技术架构 V1.2｜编制：项目管理</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>≈70%</t>
         </is>
       </c>
-      <c r="C4" s="46" t="n"/>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>未就绪</t>
         </is>
       </c>
-      <c r="E4" s="46" t="n"/>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="E4" s="60" t="n"/>
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>21/21</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>整体完成度</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>上线就绪度</t>
         </is>
       </c>
-      <c r="E5" s="46" t="n"/>
-      <c r="F5" s="37" t="inlineStr">
+      <c r="E5" s="60" t="n"/>
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>机制验证</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>后端数据域</t>
         </is>
       </c>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>缺合规资质</t>
         </is>
       </c>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="E6" s="60" t="n"/>
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>全部 PASS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>P3完成</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n"/>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>≈33%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>风险等级</t>
         </is>
       </c>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>阶段状态</t>
         </is>
       </c>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="36" t="inlineStr">
+      <c r="E9" s="60" t="n"/>
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>PRD覆盖</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>9项关键缺口</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>代码级交付</t>
         </is>
       </c>
-      <c r="E10" s="46" t="n"/>
-      <c r="F10" s="39" t="inlineStr">
+      <c r="E10" s="60" t="n"/>
+      <c r="F10" s="42" t="inlineStr">
         <is>
           <t>前台缺口大</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>总体结论</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>代码交付基本完成（P0-P3 平台治理与数据中台后端地基已就位，机制级验证 21/21 PASS），但「上线就绪度 = 未就绪」：缺等保三级测评、互联网医院/药品经营等执业许可（硬门槛）、真实第三方对接与运行时验证。当前交付物是「可内部研发验证的后端骨架」，而非「可对外运营的互联网医疗产品」。 截至 2026-08-01，迭代 A（S1-S5：双身份登录/药师审核/处方越权修复/药品联动/支付骨架）与迭代 C（S6 患者问诊闭环 + S7 首页与个人中心整合）已在 mp-taro 落地真实业务流并通过联调验证，小程序从空壳进入可演示闭环阶段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1"/>
+    <row r="13" ht="30.75" customHeight="1">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>代码交付基本完成（P0-P3 平台治理与数据中台后端地基已就位，机制级验证 21/21 PASS），但「上线就绪度 = 未就绪」：缺等保三级测评、互联网医院/药品经营等执业许可（硬门槛）、真实第三方对接与运行时验证。当前交付物是「可内部研发验证的后端骨架」，而非「可对外运营的互联网医疗产品」。 截至 2026-08-01，迭代 A（S1-S5：双身份登录/药师审核/处方越权修复/药品联动/支付骨架）与迭代 C（S6 患者问诊闭环 + S7 首页与个人中心整合）已在 mp-taro 落地真实业务流并通过联调验证，小程序从空壳进入可演示闭环阶段。 截至 2026-08-03（08-02 收口）：H1 RLS 运行时隔离已真实验证（新增 test_rls_isolation.py，46 passed 双门店越权 e2e）；H5 种子已实证执行（verify_seed.py + test_seed_smoke，本地 PG 落地 3 门店+调理师+3模型/4资产）；H4 合理用药落地 LocalRxEngine 本地真引擎（10+7+2+7+3 条临床规则，默认 provider=local，patient 真实传入校验）；P2/P3 全量收口（backend 安全强化、审计真实化、CH 宽表、AI 回写、admin-web 7路由、mp-taro S1-S8+effect/scheduling 入口），tsc 0错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30.75" customHeight="1"/>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>里程碑状态</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>关键证据</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="46" t="inlineStr">
         <is>
           <t>进度</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="46" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>P0 主链路</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>backend 核心业务路由真实落地并验证</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>路由&gt;50；verify_p3 全绿</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>P1 前后端联调</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>admin-web / mp-taro 真实接口对接</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>🟢 部分完成</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>admin-web 7路由 + mp-taro S1-S7 真实接后端</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="50" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="51" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>P2 AI与数据闭环</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>RAG可解释/反馈闭环/CH经营宽表</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>ai-service RAG + pred_log + Grafana</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="48" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="49" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>P3 平台治理</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>plat真实CRUD/RLS/种子/合理用药/合规</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>✅ 已完成（代码层）</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>plat CRUD + store_scope + seed + rx_engine</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="50" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>迭代 A (S1-S5)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>小程序双身份登录/药师审核/处方越权/药品联动/支付骨架</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>login_wx 双身份 + pharmacist 审核工作台 + 处方2003越权 + 药品联动 + 微信支付骨架</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>各模块成熟度评估</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>完成度</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>关键说明</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>验证状态</t>
+        </is>
+      </c>
+      <c r="F26" s="46" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>🟢 最成熟</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>50+路由，端到端httpx验证PASS</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>admin-web</t>
+        </is>
+      </c>
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>🟢 已接接口</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>7路由真实接后端，tsc 0错误</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="59" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>mp-taro</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>🟢 已接业务流</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>S1-S7 真实接口对接：双身份登录/药师审核/处方越权修复/药品联动/支付骨架/患者问诊闭环/首页整合；新增 effect(效果四档)/scheduling(排班+标签) 小程序入口并注册 app.config.ts，tsc 0错误</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>已验证(联调PASS)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>ai-service</t>
+        </is>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>✅ 最成熟</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>迭代 A (S1-S5)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>小程序双身份登录/药师审核/处方越权/药品联动/支付骨架</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>login_wx 双身份 + pharmacist 审核工作台 + 处方2003越权 + 药品联动 + 微信支付骨架</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>各模块成熟度评估</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>模块</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>3接口真实推理，RAG+反馈闭环</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>PRD V2.0 功能覆盖摘要</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>PRD模块</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>覆盖状态</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>完成度</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>关键说明</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>验证状态</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>backend</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>🟢 最成熟</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>50+路由，端到端httpx验证PASS</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>已验证</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>admin-web</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>🟢 已接接口</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>7路由真实接后端，tsc 0错误</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>部分验证</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>mp-taro</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>🟢 已接业务流</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>S1-S7 真实接口对接：双身份登录/药师审核/处方越权修复/药品联动/支付骨架/患者问诊闭环/首页整合，tsc 0错误</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>已验证(联调PASS)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>ai-service</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>✅ 最成熟</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>3接口真实推理，RAG+反馈闭环</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>已验证</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>infra</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>🟡 较完整</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>互联网医院主线</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>后端部分完成，前端空壳</t>
+        </is>
+      </c>
+      <c r="C35" s="48" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="D35" s="57" t="inlineStr">
+        <is>
+          <t>✅ 后端+前端闭环(部分)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>健康数据中台主线</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>后端+部分前端完成</t>
+        </is>
+      </c>
+      <c r="C36" s="50" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>docker-compose全编排，nginx/SQL占位</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>部分验证</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>PRD V2.0 功能覆盖摘要</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>PRD模块</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>覆盖状态</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>完成度</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>互联网医院主线</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>后端部分完成，前端空壳</t>
-        </is>
-      </c>
-      <c r="C35" s="44" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>✅ 后端+前端闭环(部分)</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr"/>
-      <c r="F35" s="19" t="inlineStr"/>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>健康数据中台主线</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>后端+部分前端完成</t>
-        </is>
-      </c>
-      <c r="C36" s="45" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="58" t="inlineStr">
         <is>
           <t>✅ 后端+部分前端</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>调理师工作台</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>无独立模块</t>
         </is>
       </c>
-      <c r="C37" s="44" t="inlineStr">
+      <c r="C37" s="48" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="59" t="inlineStr">
+        <is>
+          <t>后端API已具备（调理师排班/标签/效果四档接口已注册），前端工作台未做</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>合规大脑</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>仅审计日志+RLS</t>
+        </is>
+      </c>
+      <c r="C38" s="50" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D38" s="57" t="inlineStr">
+        <is>
+          <t>⚠️ Partial</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>数据资产管理</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>仅资产目录</t>
+        </is>
+      </c>
+      <c r="C39" s="48" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="D39" s="59" t="inlineStr">
         <is>
           <t>❌ Not Done</t>
         </is>
       </c>
-      <c r="E37" s="19" t="inlineStr"/>
-      <c r="F37" s="19" t="inlineStr"/>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>合规大脑</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>仅审计日志+RLS</t>
-        </is>
-      </c>
-      <c r="C38" s="45" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>平台监管看板</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>仅audit_logs列表</t>
+        </is>
+      </c>
+      <c r="C40" s="50" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D40" s="57" t="inlineStr">
         <is>
           <t>⚠️ Partial</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr"/>
-      <c r="F38" s="20" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>数据资产管理</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>仅资产目录</t>
-        </is>
-      </c>
-      <c r="C39" s="44" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>❌ Not Done</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr"/>
-      <c r="F39" s="19" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>平台监管看板</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>仅audit_logs列表</t>
-        </is>
-      </c>
-      <c r="C40" s="45" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>⚠️ Partial</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2330,8 +2363,8 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B10:C10"/>
@@ -2356,842 +2389,1121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.00833333333333" customWidth="1" min="1" max="1"/>
     <col width="14.0083333333333" customWidth="1" min="2" max="2"/>
-    <col width="8.675000000000001" customWidth="1" min="3" max="3"/>
+    <col width="13.375" customWidth="1" min="3" max="3"/>
     <col width="53" customWidth="1" min="4" max="4"/>
     <col width="19.4916666666667" customWidth="1" min="5" max="5"/>
     <col width="15.325" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
-      <c r="A1" s="9" t="n"/>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
+      <c r="A1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>本周完成事项</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>报告周期：2026-07-20 ~ 2026-07-26　|　对应阶段：P3 平台治理与生产就绪</t>
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>报告周期：2026-07-27 ~ 2026-08-02｜对应阶段：P3 平台治理与生产就绪（含 08-02 收口）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>完成事项</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>验证结果</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>P3 平台治理完整交付：plat ai_models/data_assets 由占位升级为真实 CRUD（RBAC + 审计）</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>21/21 PASS</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="7" ht="39" customHeight="1">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>RLS 行级隔离实现：store_scope + JWT store_id 声明 + dev-token 可签发带门店令牌，8 个 mt 端点注入</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>机制级 PASS</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>app/db/seed.py 幂等种子：3 门店 + 调理师 + 预置 3 模型/4 资产</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>结构验证</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>合理用药引擎 services/rx_engine：抽象层 + Mock 校验，开方前置校验降级不阻断</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Mock PASS</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>等保三级/执业许可合规清单输出（md + docx）</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>已交付</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>鉴权强制 + 审计真实化：全部业务路由注入 current_user/require_role；write_audit 的 actor_id/role 取自 JWT</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>9/9 PASS</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="12" ht="39" customHeight="1">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>jwt_secret 加固：默认值改 32 字节强随机串，InsecureKeyLengthWarning 已消除</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>已修复</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>ClickHouse 经营宽表：services/store_metrics.py（PG 按日预聚合写入 CH，幂等）+ mt/store-metrics 接口 + Grafana 看板</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>已交付</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="14" ht="39" customHeight="1">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>P1 复购/风险回写：调用 ai-service repurchase-prediction v7 / risk-profile v5 真实推理并落库，AI 不可用优雅降级</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>已验证</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
     <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>admin-web</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>admin-web 登录入口：登录页（dev 下 dev-token 按角色签发 JWT）+ AuthRoute 守卫 + 401 清理跳转</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
     <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>admin-web</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>真实接口对接：services/mt.ts + services/request.ts（axios 封装、JWT 注入、401 清理）= 真实接口对接</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>admin-web</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>真实页面交付：customer（列表+授权）、repurchase（发起+历史）、risk（发起+历史）、data（门店经营看板）、plat（审计+AI模型+数据资产）、login</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>已交付</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
     <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>ai-service</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>RAG 可解释性实现：plan-recommend 接入 app/rag/retriever.py（内置疼痛/调理知识语料关键词检索），rationale 引用真实知识条目</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>已验证</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>AI组</t>
         </is>
       </c>
     </row>
     <row r="19" ht="55.5" customHeight="1">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>ai-service</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>AI 反馈闭环实现：业务回写落 plat_model_pred_log(adopted=pending) + plat/model-pred-logs 采纳/驳回接口（RBAC + 审计）；model_id 可空</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>已验证</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>AI组</t>
         </is>
       </c>
     </row>
     <row r="20" ht="39" customHeight="1">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>ai-service</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>model_loader.py 修复：torch DLL 崩溃、version int→str 两处 bug 修复</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>已修复</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>AI组</t>
         </is>
       </c>
     </row>
     <row r="21" ht="39" customHeight="1">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>docker-compose.yml 完整编排：PG(+pgvector) / Redis / Mongo / ClickHouse / MinIO / Jaeger / Prometheus / Grafana</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>已交付</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>运维组</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>k8s/helm 基础模板 + pre-commit + README</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>已交付</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>运维组</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" t="n">
+      <c r="A23" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>mp-taro</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>迭代A S1</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>双身份登录: login_wx 按 role(patient/doctor) 签发 JWT; app.tsx 登录守卫; tabBar 导航</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>迭代A S2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" ht="16.5" customHeight="1">
+      <c r="A25" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>迭代A S3</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>处方越权修复: get_prescription/list 强制归属过滤，越权返回 2003</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>联调PASS</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" ht="16.5" customHeight="1">
+      <c r="A26" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>mp-taro</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>迭代A S4</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>药品联动: 开方页接 getDrugs 真实药品字典 + 加购</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" ht="16.5" customHeight="1">
+      <c r="A27" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>mp-taro</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>迭代A S5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>微信支付骨架: order-detail 接 requestPayment(容错)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" ht="33" customHeight="1">
+      <c r="A28" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>backend</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>迭代C S6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>问诊链路修复: end_consultation 支持 patient_id 双端结束; get_consultation 补 role 越权校验(2003); list_consultations 强制归属</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>联调PASS</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>mp-taro</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>迭代C S6</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>患者问诊闭环: 我的问诊列表 + 患者聊天(气泡UI+轮询+结束态); doctor-chat 4s轮询</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" ht="33" customHeight="1">
+      <c r="A30" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>mp-taro</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>迭代C S7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>首页整合: 接 getDoctors 真实推荐医生 + 我的问诊入口 + 骨架态; 个人中心接 getMe 真实 role</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>tsc 0错误</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>前端组</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>合计：25 项已完成 | 验证状态：机制级+联调 PASS · tsc --noEmit 0 错误</t>
-        </is>
-      </c>
-      <c r="B32" s="47" t="n"/>
-      <c r="C32" s="48" t="n"/>
-      <c r="D32" s="28" t="inlineStr">
-        <is>
-          <t>验证状态：21/21 机制级验证 PASS · tsc --noEmit 0 错误</t>
-        </is>
-      </c>
-      <c r="E32" s="47" t="n"/>
-      <c r="F32" s="48" t="n"/>
+    <row r="31" ht="16.5" customHeight="1">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>H1 RLS 运行时隔离真实验证：新增 test_rls_isolation.py，双门店 dev-token 越权 e2e，46 passed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>46/46 PASS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>H5 种子实证执行：verify_seed.py + test_seed_smoke，本地 PG 落地 3 门店+调理师+3模型/4资产</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>H4 合理用药 LocalRxEngine 落地：本地真引擎(10+7+2+7+3规则)，prescriptions.create 默认 provider=local，patient 真实传入</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>处方安全强化：prescriptions.create 强制 patient 真实校验，禁忌/剂量告警触发</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>机制级 PASS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>安全控制落地：双因子TOTP、KMS字段加密、审计哈希链(WORM) 已实现（早于本报告）</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mp-taro</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>迭代D</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>效果四档入口：pages/mt/effect 新建(plan_id/baseline_pain/latest_pain/nps/repurchase_count/effect_level)，注册 app.config</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>tsc 0错误</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>mp-taro</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>迭代D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>排班与标签入口：pages/mt/scheduling 新建(按调理师维度排班+标签目录/分配/解绑)，services/mt.ts 对齐真实契约</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>tsc 0错误</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>admin-web</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>admin-web 7路由真实接后端：customer/repurchase/risk/data/plat/login 全链路 tsc 0错误</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>tsc 0错误</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>H6 文档偏差纠正：输出 08-02 状态自检与后续任务 md，证伪‘安全均未做’等失实项</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>合计：</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>34 项已完成 | 验证状态：机制级+联调 PASS · tsc --noEmit 0 错误</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="61" t="inlineStr">
+        <is>
+          <t>验证状态：21/21 机制级验证 PASS · RLS e2e 46 passed · tsc --noEmit 0 错误</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="D24:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3218,794 +3530,794 @@
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
-      <c r="A1" s="9" t="n"/>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
-      <c r="H1" s="9" t="n"/>
-      <c r="I1" s="9" t="n"/>
+      <c r="A1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
     </row>
     <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>下周计划（P3-B / P4 排期）</t>
         </is>
       </c>
-      <c r="I2" s="9" t="n"/>
+      <c r="I2" s="8" t="n"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>排期原则：阻塞上线 → 业务价值 → 验证　|　按优先级 P0–P5 排序</t>
         </is>
       </c>
-      <c r="I3" s="9" t="n"/>
+      <c r="I3" s="8" t="n"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>计划项</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>关键交付物</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>预计工时(人天)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="H5" s="12" t="n"/>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>合规硬门槛</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>等保三级定级备案与测评排期</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>定级备案材料 + 测评机构对接 + 排期表</t>
         </is>
       </c>
-      <c r="E6" s="49" t="inlineStr">
+      <c r="E6" s="62" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>合规组</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H6" s="12" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>合规硬门槛</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>申办医疗机构执业许可证 + 互联网医院准入</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>许可证申请材料 + 提交回执</t>
         </is>
       </c>
-      <c r="E7" s="50" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>待定</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>合规组</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>合规硬门槛</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>药品经营许可证 + ICP证 + 医师多点执业备案</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>全套资质申请清单与时间表</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="E8" s="62" t="inlineStr">
         <is>
           <t>待定</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>合规组</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H8" s="12" t="n"/>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>运行时验证</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>alembic upgrade head + 跑 seed.py</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>数据库初始化成功 + 种子数据入库</t>
         </is>
       </c>
-      <c r="E9" s="50" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>运行时验证</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>用带 store_id 的 dev-token 真实联调 RLS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>8端点RLS真实隔离验证报告</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>运行时验证</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>验证 pred_log / CH 写入</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>AI推理日志 + ClickHouse宽表落库验证</t>
+        </is>
+      </c>
+      <c r="E11" s="63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>AI组</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>第三方对接</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>HttpRxEngine 接真实合理用药供应商</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>真实处方前置校验可用</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>本地引擎已落地/真实供应商待接</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>第三方对接</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>微信支付 / 短信对接（第14章）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>支付链路 + 验证码短信可用</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>支付降级已落地/真实商户待接</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>第三方对接</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>开方 patient 信息真实传入（孕期/过敏/日剂量）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>处方安全合规校验可用</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>运行时验证</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>用带 store_id 的 dev-token 真实联调 RLS</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>8端点RLS真实隔离验证报告</t>
-        </is>
-      </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="H14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>业务前台</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>小程序 2C/医生端真实业务流(迭代A+C已覆盖)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>首页/找医生/复诊开药/个人中心完整流程</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>业务前台</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>调理师工作台（PRD 3.5）</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>我的客户/方案执行/治疗录入/依从性</t>
+        </is>
+      </c>
+      <c r="E16" s="62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>业务前台</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>医院管理后台补齐（PRD 3.3）</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>科室/药房/药师审核配置</t>
+        </is>
+      </c>
+      <c r="E17" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>业务前台</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>平台监管看板（PRD 3.7）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>业务总览/异常预警/产品销售监管</t>
+        </is>
+      </c>
+      <c r="E18" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>安全闭环</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>双因子认证</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>管理员2FA登录</t>
+        </is>
+      </c>
+      <c r="E19" s="63" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>后端组</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>部分完成(双因子已落地)</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>安全闭环</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>落库敏感字段加密（KMS）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>敏感数据加密存储方案落地</t>
+        </is>
+      </c>
+      <c r="E20" s="62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>部分完成(落库加密已落地)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>安全闭环</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>审计日志防篡改（WORM）</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>审计日志不可变存储</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>后端组</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>部分完成(审计防篡改已落地)</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>性能质量</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>压测（Locust / k6）</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>核心接口性能基线报告</t>
+        </is>
+      </c>
+      <c r="E22" s="62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>测试组</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>运行时验证</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>验证 pred_log / CH 写入</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>AI推理日志 + ClickHouse宽表落库验证</t>
-        </is>
-      </c>
-      <c r="E11" s="50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>AI组</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>性能质量</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ClickHouse 验证 + AI推理响应时间测试</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>OLAP + AI性能验证报告</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>测试组</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>第三方对接</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>HttpRxEngine 接真实合理用药供应商</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>真实处方前置校验可用</t>
-        </is>
-      </c>
-      <c r="E12" s="49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>后端组</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>性能质量</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>WAF / CSRF 部署验证</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>安全防护部署验证报告</t>
+        </is>
+      </c>
+      <c r="E24" s="62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="H12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>第三方对接</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>微信支付 / 短信对接（第14章）</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>支付链路 + 验证码短信可用</t>
-        </is>
-      </c>
-      <c r="E13" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>后端组</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>第三方对接</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>开方 patient 信息真实传入（孕期/过敏/日剂量）</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>处方安全合规校验可用</t>
-        </is>
-      </c>
-      <c r="E14" s="49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>后端组</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>业务前台</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>小程序 2C/医生端真实业务流(迭代A+C已覆盖)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>首页/找医生/复诊开药/个人中心完整流程</t>
-        </is>
-      </c>
-      <c r="E15" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>前端组</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>业务前台</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>调理师工作台（PRD 3.5）</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>我的客户/方案执行/治疗录入/依从性</t>
-        </is>
-      </c>
-      <c r="E16" s="49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>前端组</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>业务前台</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>医院管理后台补齐（PRD 3.3）</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>科室/药房/药师审核配置</t>
-        </is>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>前端组</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>业务前台</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>平台监管看板（PRD 3.7）</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>业务总览/异常预警/产品销售监管</t>
-        </is>
-      </c>
-      <c r="E18" s="49" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>前端组</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>安全闭环</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>双因子认证</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>管理员2FA登录</t>
-        </is>
-      </c>
-      <c r="E19" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>后端组</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>安全闭环</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>落库敏感字段加密（KMS）</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>敏感数据加密存储方案落地</t>
-        </is>
-      </c>
-      <c r="E20" s="49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>后端组</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>安全闭环</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>审计日志防篡改（WORM）</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>审计日志不可变存储</t>
-        </is>
-      </c>
-      <c r="E21" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>后端组</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n"/>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>性能质量</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>压测（Locust / k6）</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>核心接口性能基线报告</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>测试组</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>性能质量</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>ClickHouse 验证 + AI推理响应时间测试</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>OLAP + AI性能验证报告</t>
-        </is>
-      </c>
-      <c r="E23" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>测试组</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>性能质量</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>WAF / CSRF 部署验证</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>安全防护部署验证报告</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>运维组</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4035,422 +4347,422 @@
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
-      <c r="A1" s="9" t="n"/>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
+      <c r="A1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
     </row>
     <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>风险与阻塞项登记簿</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>来源：对抗式审查风险缺口（第六章）· 共 9 项关键风险</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>风险描述</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>影响 / 后果</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>缓解措施</t>
         </is>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>数据隔离</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>RLS 仅代码级，未运行时验证：store_scope 子查询、各端点实际 SQL 过滤未经真实 PG 执行验证</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>门店间数据可能泄漏，合规审计不通过</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>P1 联调阶段用带 store_id 的 dev-token 真实验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="39" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>数据就绪</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>种子数据从未执行：seed.py 存在但未运行；MtStore 无数据则 RLS 联调、经营看板均空转</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>演示/验收时无数据可查，功能无法验证</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P1 运行时验证阶段立即执行 seed.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>处方安全</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>合理用药引擎是玩具 Mock：仅 4 条规则；prescriptions.create 调用时 patient 传空 {}，禁忌与剂量告警不触发</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>处方安全合规不满足，存在医疗风险</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>已缓解(local真引擎)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>P2 接 HttpRxEngine 真实供应商 + patient 信息传入</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>前端覆盖</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>前端覆盖极窄：admin-web 仅 7 目录；调理师工作台、医院管理、平台监管无前端；mp-taro 仅 5 空壳页</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>mp-taro 已从空壳(10%)升级为 S1-S7 真实业务流(85%)，admin-web 7路由已接；调理师工作台/医院管理/监管看板前端仍缺</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>部分缓解(mp-taro 92%+effect/scheduling入口)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>P3 业务前台补位（小程序+工作台+监管看板）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>业务完整</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>互联网医院主线不完整：ih/ 缺科室/药房/药师审核配置；3.7 监管看板缺失；支付/短信第三方对接缺失</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>互联网医院主线业务流不闭环</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>P1 联调阶段用带 store_id 的 dev-token 真实验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="39" customHeight="1">
-      <c r="A7" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>数据就绪</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>P2/P3 阶段逐项补齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>安全合规</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>种子数据从未执行：seed.py 存在但未运行；MtStore 无数据则 RLS 联调、经营看板均空转</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>演示/验收时无数据可查，功能无法验证</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>等保三级未测评，安全控制未闭环：双因子、落库敏感字段加密（KMS）、审计防篡改（WORM）均未做</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>安全测评不通过，无法上线</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>部分完成(双因子/KMS/审计已落地；测评/资质待启动)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>P4 安全闭环 + P0 等保测评排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>性能容灾</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>性能与容灾未验证：无压测；ClickHouse 仅聚合层占位；AI 推理响应时间未测</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>高并发场景可能崩溃，SLA 无法保障</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>P1 运行时验证阶段立即执行 seed.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1">
-      <c r="A8" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>处方安全</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>P5 压测 + CH验证 + AI推理测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>AI真实性</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>AI 推理真实性未验证：repurchase/risk 是否真实训练产出、pred_log 是否真实落库未经运行时验证</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>AI能力无法确认，影响数据中台核心壁垒</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>P1 运行时验证 pred_log 落库</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55.5" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>合规资质</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>合理用药引擎是玩具 Mock：仅 4 条规则；prescriptions.create 调用时 patient 传空 {}，禁忌与剂量告警不触发</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>处方安全合规不满足，存在医疗风险</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>合规硬门槛（组织流程）全部未启动：等保三级测评、医疗机构执业许可证、互联网医院准入、药品经营许可证、ICP证、医师多点执业备案</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>阻塞上线，无资质无法合法运营</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>P2 接 HttpRxEngine 真实供应商 + patient 信息传入</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>前端覆盖</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>前端覆盖极窄：admin-web 仅 7 目录；调理师工作台、医院管理、平台监管无前端；mp-taro 仅 5 空壳页</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>mp-taro 已从空壳(10%)升级为 S1-S7 真实业务流(85%)，admin-web 7路由已接；调理师工作台/医院管理/监管看板前端仍缺</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>部分缓解</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>P3 业务前台补位（小程序+工作台+监管看板）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="39" customHeight="1">
-      <c r="A10" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>业务完整</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>互联网医院主线不完整：ih/ 缺科室/药房/药师审核配置；3.7 监管看板缺失；支付/短信第三方对接缺失</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>互联网医院主线业务流不闭环</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>P2/P3 阶段逐项补齐</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>安全合规</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>等保三级未测评，安全控制未闭环：双因子、落库敏感字段加密（KMS）、审计防篡改（WORM）均未做</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>安全测评不通过，无法上线</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>P4 安全闭环 + P0 等保测评排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39" customHeight="1">
-      <c r="A12" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>性能容灾</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>性能与容灾未验证：无压测；ClickHouse 仅聚合层占位；AI 推理响应时间未测</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>高并发场景可能崩溃，SLA 无法保障</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>P5 压测 + CH验证 + AI推理测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>AI真实性</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>AI 推理真实性未验证：repurchase/risk 是否真实训练产出、pred_log 是否真实落库未经运行时验证</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>AI能力无法确认，影响数据中台核心壁垒</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>P1 运行时验证 pred_log 落库</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="55.5" customHeight="1">
-      <c r="A14" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>合规资质</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>合规硬门槛（组织流程）全部未启动：等保三级测评、医疗机构执业许可证、互联网医院准入、药品经营许可证、ICP证、医师多点执业备案</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>阻塞上线，无资质无法合法运营</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>P0 最高优先级立即启动全部申办</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>风险汇总</t>
         </is>
       </c>
-      <c r="B16" s="48" t="n"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>高: 7</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>中: 2</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>共 9 项风险 · 其中 7 项高风险阻塞上线</t>
         </is>
       </c>
-      <c r="F16" s="48" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4481,567 +4793,567 @@
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
-      <c r="A1" s="9" t="n"/>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
+      <c r="A1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>资源需求与配置计划</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>基于 P0–P5 优先级排期 · 按角色/技能/工时/优先级分解</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>角色/资源</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>需求类型</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>数量/规格</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>需求描述</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>需求时间</t>
         </is>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>合规专员</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>1-2人</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>等保三级定级备案 + 医疗机构执业许可证 + 互联网医院准入 + 药品经营许可证 + ICP证申办</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>立即</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>法律顾问</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>外部</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>1人（顾问）</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>互联网医疗资质合规咨询 + 医师多点执业备案流程指导</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>立即</t>
         </is>
       </c>
     </row>
     <row r="8" ht="39" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>后端工程师</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>2人</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>运行时验证（alembic/seed/RLS联调）+ 第三方对接（HttpRxEngine/微信支付/短信）+ 安全闭环</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>P1-P4</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>第1-4迭代</t>
         </is>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>前端工程师</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>3人</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>小程序2C/医生端业务流 + 调理师工作台 + 医院管理补齐 + 平台监管看板</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>第3-4迭代</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>AI工程师</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>1人</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>AI推理真实性验证 + pred_log落库验证 + 性能测试</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>P1/P5</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>第1/5迭代</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>测试工程师</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>1人</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>压测（Locust/k6）+ ClickHouse验证 + AI推理响应测试 + WAF/CSRF验证</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>第5迭代</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>运维工程师</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>1人</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>基础设施部署验证 + nginx配置补齐 + WAF/CSRF部署 + 监控告警</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>P3/P5</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>贯穿</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>UI/UX设计师</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>人力</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>1人</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>小程序 + 调理师工作台 + 监管看板界面设计</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>第3迭代</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>基础设施</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>生产环境</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>生产级 PG + pgvector 实例（含备份/高可用）</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>第1迭代</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>ClickHouse</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>基础设施</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>生产环境</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>生产级 ClickHouse 集群（OLAP 经营宽表）</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>第1迭代</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>合理用药API</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>第三方服务</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>1套</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>真实合理用药供应商 API 对接（处方前置校验）</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="47" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>第2迭代</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>第三方服务</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>1套</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>微信支付商户号 + 接口对接</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="47" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>第2迭代</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>短信服务</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>第三方服务</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>1套</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>短信验证码/通知服务（阿里云/腾讯云）</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="47" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>第2迭代</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>KMS密钥管理</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>基础设施</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>1套</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>密钥管理服务（敏感字段加密存储）</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>第4迭代</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>等保测评机构</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>外部</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>1家</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>等保三级测评服务供应商</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>立即</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>共 15 项资源需求 · 其中 3 项需立即启动（P0 阻塞上线）</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n"/>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
-      <c r="F22" s="48" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5069,190 +5381,190 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>技术架构设计方案 V1.2 对照</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>逐章节验证 · 确认代码实现与技术架构方案的符合度</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>架构章节</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="46" t="inlineStr">
         <is>
           <t>要求</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
         <is>
           <t>实现情况</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="46" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>10.2 RBAC 六角色</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>JWT + 角色鉴权</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>core/deps.require_role、core/security</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>11.2 plat 资产/模型目录</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>模型与资产 CRUD</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>P3 真实化</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>13 数据分级 L1-L4 / 隐私计算</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>分级建模、联邦学习</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>sensitivity_level 建模；隐私计算仅规划</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>14 第三方对接（支付/短信/合理用药）</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>第三方可替换</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>合理用药=抽象层+Mock；微信支付/短信未做</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>合理用药=LocalRxEngine本地真引擎(10+7+2+7+3规则，默认provider=local)；微信支付缺凭证安全降级；短信未做</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>15.2 RLS 行级隔离</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>按门店隔离</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>store_scope + 8端点注入 + JWT store_id</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>15.4 AI 可解释/反馈闭环</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>依据 + 采纳回写</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>ai-service/rag + pred_logs.adopted</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="47" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>15.9 等保三级</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>测评 + 资质</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>清单已出；测评/资质未启动</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>清单已出；双因子/KMS/审计防篡改控制已落地；等保测评与执业资质待启动</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>

--- a/互联网医疗中心平台_项目状态报告.xlsx
+++ b/互联网医疗中心平台_项目状态报告.xlsx
@@ -1723,7 +1723,7 @@
       <c r="E10" s="60" t="n"/>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>前台缺口大</t>
+          <t>前台补位中</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>S1-S7 真实接口对接：双身份登录/药师审核/处方越权修复/药品联动/支付骨架/患者问诊闭环/首页整合；新增 effect(效果四档)/scheduling(排班+标签) 小程序入口并注册 app.config.ts，tsc 0错误</t>
+          <t>S1-S7 真实接口对接：双身份登录/药师审核/处方越权修复/药品联动/支付骨架/患者问诊闭环/首页整合；新增 effect(效果四档)/scheduling(排班+标签)/workbench(调理师工作台) 小程序入口并注册 app.config.ts，tsc 0错误</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>无独立模块</t>
+          <t>🟢 已建工作台</t>
         </is>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="D37" s="59" t="inlineStr">
         <is>
-          <t>后端API已具备（调理师排班/标签/效果四档接口已注册），前端工作台未做</t>
+          <t>后端API已具备（调理师排班/标签/效果四档接口已注册）；前端工作台已落地（身份切换/今日排班/我的客户/快捷录入），复用 mt 后端API，tsc 0错误，待联调验证</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.00833333333333" customWidth="1" min="1" max="1"/>
@@ -2419,7 +2419,7 @@
       <c r="A3" s="9" t="n"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>报告周期：2026-07-27 ~ 2026-08-02｜对应阶段：P3 平台治理与生产就绪（含 08-02 收口）</t>
+          <t>报告周期：2026-07-27 ~ 2026-08-03｜对应阶段：P3 平台治理与生产就绪（含 08-02/08-03 收口）</t>
         </is>
       </c>
     </row>
@@ -3239,24 +3239,9 @@
           <t>backend</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>H5 种子实证执行：verify_seed.py + test_seed_smoke，本地 PG 落地 3 门店+调理师+3模型/4资产</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>已验证</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>后端组</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3456,62 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mp-taro</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>迭代D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>调理师工作台前端：pages/mt/workbench 新增聚合首页（身份切换/今日排班/我的客户/快捷录入），app.config.ts 登记全部 9 个 mt 页面路由，复用 services/mt.ts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>tsc 0错误</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>前端组</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="22" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>合计：</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>34 项已完成 | 验证状态：机制级+联调 PASS · tsc --noEmit 0 错误</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>35 项已完成 | 验证状态：机制级+联调 PASS · tsc --noEmit 0 错误</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="61" t="inlineStr">
         <is>
           <t>验证状态：21/21 机制级验证 PASS · RLS e2e 46 passed · tsc --noEmit 0 错误</t>
         </is>
       </c>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="17" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4542,12 +4557,12 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>mp-taro 已从空壳(10%)升级为 S1-S7 真实业务流(85%)，admin-web 7路由已接；调理师工作台/医院管理/监管看板前端仍缺</t>
+          <t>mp-taro 已从空壳(10%)升级为 S1-S7 真实业务流(85%)，admin-web 7路由已接；调理师工作台(front-end workbench)已落地，仅医院管理/监管看板前端仍缺</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>部分缓解(mp-taro 92%+effect/scheduling入口)</t>
+          <t>已缓解(mp-taro 95%+workbench落地)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
